--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755621354_individual_h_10.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755621354_individual_h_10.xlsx
@@ -658,7 +658,7 @@
         <v>0.04969362208244506</v>
       </c>
       <c r="C2" t="n">
-        <v>62127720</v>
+        <v>6212772</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>62127720</v>
+        <v>6212772</v>
       </c>
       <c r="K2" t="n">
-        <v>41965279</v>
+        <v>3675351</v>
       </c>
       <c r="L2" t="n">
-        <v>23548582</v>
+        <v>1793097</v>
       </c>
       <c r="M2" t="n">
-        <v>5829211</v>
+        <v>383554</v>
       </c>
       <c r="N2" t="n">
-        <v>308350</v>
+        <v>14506</v>
       </c>
       <c r="O2" t="n">
-        <v>3545347</v>
+        <v>245334</v>
       </c>
       <c r="P2" t="n">
-        <v>1462232</v>
+        <v>108077</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999169111251831</v>
+        <v>0.9998278021812439</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8555724024772644</v>
+        <v>0.7492419481277466</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7209947109222412</v>
+        <v>0.5487773418426514</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6365320086479187</v>
+        <v>0.4196433126926422</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4535872936248779</v>
+        <v>0.2146810740232468</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6956400871276855</v>
+        <v>0.4815673530101776</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7590399384498596</v>
+        <v>0.560934841632843</v>
       </c>
       <c r="X2" t="n">
-        <v>62127720</v>
+        <v>6212772</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>62127720</v>
+        <v>6212772</v>
       </c>
       <c r="AF2" t="n">
-        <v>40931866</v>
+        <v>3625657</v>
       </c>
       <c r="AG2" t="n">
-        <v>21825235</v>
+        <v>1702389</v>
       </c>
       <c r="AH2" t="n">
-        <v>5311771</v>
+        <v>359888</v>
       </c>
       <c r="AI2" t="n">
-        <v>286298</v>
+        <v>13986</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3264326</v>
+        <v>229809</v>
       </c>
       <c r="AK2" t="n">
-        <v>1375892</v>
+        <v>101680</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.8289598822593689</v>
+        <v>0.7342748641967773</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.6811686158180237</v>
+        <v>0.5313179492950439</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.573558509349823</v>
+        <v>0.388602614402771</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.3239471316337585</v>
+        <v>0.1582520604133606</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.6425155401229858</v>
+        <v>0.4523318409919739</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.7119272947311401</v>
+        <v>0.5261224508285522</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.01495173573263417</v>
       </c>
       <c r="C3" t="n">
-        <v>1524</v>
+        <v>379</v>
       </c>
       <c r="D3" t="n">
-        <v>41965279</v>
+        <v>3675351</v>
       </c>
       <c r="E3" t="n">
-        <v>6484075</v>
+        <v>1059578</v>
       </c>
       <c r="F3" t="n">
-        <v>336181</v>
+        <v>77365</v>
       </c>
       <c r="G3" t="n">
-        <v>43453</v>
+        <v>7536</v>
       </c>
       <c r="H3" t="n">
-        <v>27267</v>
+        <v>8986</v>
       </c>
       <c r="I3" t="n">
-        <v>3908</v>
+        <v>1467</v>
       </c>
       <c r="J3" t="n">
-        <v>98571119</v>
+        <v>9856558</v>
       </c>
       <c r="K3" t="n">
-        <v>104758232</v>
+        <v>10009663</v>
       </c>
       <c r="L3" t="n">
-        <v>119125653</v>
+        <v>11303629</v>
       </c>
       <c r="M3" t="n">
-        <v>148047828</v>
+        <v>14600262</v>
       </c>
       <c r="N3" t="n">
-        <v>159443874</v>
+        <v>15927942</v>
       </c>
       <c r="O3" t="n">
-        <v>154054819</v>
+        <v>15294638</v>
       </c>
       <c r="P3" t="n">
-        <v>158305196</v>
+        <v>15791999</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.858858585357666</v>
+        <v>0.7608379721641541</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7253375649452209</v>
+        <v>0.5446123480796814</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6249410510063171</v>
+        <v>0.4081699252128601</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3469780087471008</v>
+        <v>0.1622703969478607</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6954383850097656</v>
+        <v>0.479498565196991</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7558265924453735</v>
+        <v>0.5576584935188293</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>40931866</v>
+        <v>3625657</v>
       </c>
       <c r="Z3" t="n">
-        <v>7260474</v>
+        <v>1076099</v>
       </c>
       <c r="AA3" t="n">
-        <v>475615</v>
+        <v>95172</v>
       </c>
       <c r="AB3" t="n">
-        <v>149460</v>
+        <v>19777</v>
       </c>
       <c r="AC3" t="n">
-        <v>38103</v>
+        <v>11762</v>
       </c>
       <c r="AD3" t="n">
-        <v>6169</v>
+        <v>2195</v>
       </c>
       <c r="AE3" t="n">
-        <v>98576280</v>
+        <v>9857628</v>
       </c>
       <c r="AF3" t="n">
-        <v>103396799</v>
+        <v>9927657</v>
       </c>
       <c r="AG3" t="n">
-        <v>118022678</v>
+        <v>11276274</v>
       </c>
       <c r="AH3" t="n">
-        <v>147427074</v>
+        <v>14564488</v>
       </c>
       <c r="AI3" t="n">
-        <v>159217845</v>
+        <v>15906614</v>
       </c>
       <c r="AJ3" t="n">
-        <v>153789783</v>
+        <v>15280508</v>
       </c>
       <c r="AK3" t="n">
-        <v>158212649</v>
+        <v>15785012</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.8377088308334351</v>
+        <v>0.7505507469177246</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.6722554564476013</v>
+        <v>0.5170618891716003</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.5694671273231506</v>
+        <v>0.3829850554466248</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.3221634924411774</v>
+        <v>0.1564534604549408</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.6403146386146545</v>
+        <v>0.4491553604602814</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.711197555065155</v>
+        <v>0.524651050567627</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.09930228843434777</v>
       </c>
       <c r="C4" t="n">
-        <v>591</v>
+        <v>139</v>
       </c>
       <c r="D4" t="n">
-        <v>6598400</v>
+        <v>1117489</v>
       </c>
       <c r="E4" t="n">
-        <v>23548582</v>
+        <v>1793097</v>
       </c>
       <c r="F4" t="n">
-        <v>1927678</v>
+        <v>293313</v>
       </c>
       <c r="G4" t="n">
-        <v>77780</v>
+        <v>14128</v>
       </c>
       <c r="H4" t="n">
-        <v>274387</v>
+        <v>63591</v>
       </c>
       <c r="I4" t="n">
-        <v>38269</v>
+        <v>10671</v>
       </c>
       <c r="J4" t="n">
-        <v>5161</v>
+        <v>1070</v>
       </c>
       <c r="K4" t="n">
-        <v>7084081</v>
+        <v>1230075</v>
       </c>
       <c r="L4" t="n">
-        <v>9112660</v>
+        <v>1474343</v>
       </c>
       <c r="M4" t="n">
-        <v>3328555</v>
+        <v>530446</v>
       </c>
       <c r="N4" t="n">
-        <v>371453</v>
+        <v>53064</v>
       </c>
       <c r="O4" t="n">
-        <v>1551178</v>
+        <v>264115</v>
       </c>
       <c r="P4" t="n">
-        <v>464191</v>
+        <v>84596</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999584555625916</v>
+        <v>0.9999138712882996</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8572123050689697</v>
+        <v>0.7549954652786255</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7231596112251282</v>
+        <v>0.5466868877410889</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6306833028793335</v>
+        <v>0.4138270914554596</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3931841850280762</v>
+        <v>0.1848321855068207</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6955392360687256</v>
+        <v>0.4805307388305664</v>
       </c>
       <c r="W4" t="n">
-        <v>0.757429838180542</v>
+        <v>0.5592918992042542</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>7818406</v>
+        <v>1177970</v>
       </c>
       <c r="Z4" t="n">
-        <v>21825235</v>
+        <v>1702389</v>
       </c>
       <c r="AA4" t="n">
-        <v>2273688</v>
+        <v>306468</v>
       </c>
       <c r="AB4" t="n">
-        <v>152950</v>
+        <v>21732</v>
       </c>
       <c r="AC4" t="n">
-        <v>343900</v>
+        <v>71063</v>
       </c>
       <c r="AD4" t="n">
-        <v>51508</v>
+        <v>12806</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>8445514</v>
+        <v>1312081</v>
       </c>
       <c r="AG4" t="n">
-        <v>10215635</v>
+        <v>1501698</v>
       </c>
       <c r="AH4" t="n">
-        <v>3949309</v>
+        <v>566220</v>
       </c>
       <c r="AI4" t="n">
-        <v>597482</v>
+        <v>74392</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1816214</v>
+        <v>278245</v>
       </c>
       <c r="AK4" t="n">
-        <v>556738</v>
+        <v>91583</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.8333114385604858</v>
+        <v>0.742323637008667</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.676682710647583</v>
+        <v>0.524092972278595</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.5715054869651794</v>
+        <v>0.3857733905315399</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.323052853345871</v>
+        <v>0.1573476195335388</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.6414132118225098</v>
+        <v>0.4507379829883575</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.7115622758865356</v>
+        <v>0.5253856778144836</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>984</v>
+        <v>202</v>
       </c>
       <c r="D5" t="n">
-        <v>340810</v>
+        <v>83500</v>
       </c>
       <c r="E5" t="n">
-        <v>2138862</v>
+        <v>312123</v>
       </c>
       <c r="F5" t="n">
-        <v>5829211</v>
+        <v>383554</v>
       </c>
       <c r="G5" t="n">
-        <v>136866</v>
+        <v>17238</v>
       </c>
       <c r="H5" t="n">
-        <v>779168</v>
+        <v>120693</v>
       </c>
       <c r="I5" t="n">
-        <v>101716</v>
+        <v>22382</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>6896408</v>
+        <v>1155311</v>
       </c>
       <c r="L5" t="n">
-        <v>8917105</v>
+        <v>1499331</v>
       </c>
       <c r="M5" t="n">
-        <v>3498406</v>
+        <v>556138</v>
       </c>
       <c r="N5" t="n">
-        <v>580323</v>
+        <v>74888</v>
       </c>
       <c r="O5" t="n">
-        <v>1552656</v>
+        <v>266313</v>
       </c>
       <c r="P5" t="n">
-        <v>472381</v>
+        <v>85728</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999678730964661</v>
+        <v>0.9999334216117859</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9130046963691711</v>
+        <v>0.8515664935112</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8878076076507568</v>
+        <v>0.8149595260620117</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9575183987617493</v>
+        <v>0.9323859810829163</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9940774440765381</v>
+        <v>0.9920380115509033</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9806860089302063</v>
+        <v>0.9669934511184692</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9941720962524414</v>
+        <v>0.9894014000892639</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>444611</v>
+        <v>99186</v>
       </c>
       <c r="Z5" t="n">
-        <v>2378212</v>
+        <v>313472</v>
       </c>
       <c r="AA5" t="n">
-        <v>5311771</v>
+        <v>359888</v>
       </c>
       <c r="AB5" t="n">
-        <v>165510</v>
+        <v>18421</v>
       </c>
       <c r="AC5" t="n">
-        <v>900772</v>
+        <v>123791</v>
       </c>
       <c r="AD5" t="n">
-        <v>126741</v>
+        <v>24934</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>7929821</v>
+        <v>1205005</v>
       </c>
       <c r="AG5" t="n">
-        <v>10640452</v>
+        <v>1590039</v>
       </c>
       <c r="AH5" t="n">
-        <v>4015846</v>
+        <v>579804</v>
       </c>
       <c r="AI5" t="n">
-        <v>602375</v>
+        <v>75408</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1833677</v>
+        <v>281838</v>
       </c>
       <c r="AK5" t="n">
-        <v>558721</v>
+        <v>92125</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.8981025218963623</v>
+        <v>0.8433712720870972</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.8702204823493958</v>
+        <v>0.8076129555702209</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9504358768463135</v>
+        <v>0.9286872744560242</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9925337433815002</v>
+        <v>0.9906784892082214</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9772881269454956</v>
+        <v>0.9651481509208679</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9930589199066162</v>
+        <v>0.9885685443878174</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>1412</v>
+        <v>232</v>
       </c>
       <c r="D6" t="n">
-        <v>114970</v>
+        <v>17264</v>
       </c>
       <c r="E6" t="n">
-        <v>161608</v>
+        <v>23335</v>
       </c>
       <c r="F6" t="n">
-        <v>181253</v>
+        <v>18099</v>
       </c>
       <c r="G6" t="n">
-        <v>308350</v>
+        <v>14506</v>
       </c>
       <c r="H6" t="n">
-        <v>103433</v>
+        <v>12925</v>
       </c>
       <c r="I6" t="n">
-        <v>17647</v>
+        <v>3033</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>135685</v>
+        <v>18527</v>
       </c>
       <c r="Z6" t="n">
-        <v>161747</v>
+        <v>22938</v>
       </c>
       <c r="AA6" t="n">
-        <v>171099</v>
+        <v>17926</v>
       </c>
       <c r="AB6" t="n">
-        <v>286298</v>
+        <v>13986</v>
       </c>
       <c r="AC6" t="n">
-        <v>113385</v>
+        <v>12833</v>
       </c>
       <c r="AD6" t="n">
-        <v>20459</v>
+        <v>3184</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>406</v>
+        <v>83</v>
       </c>
       <c r="D7" t="n">
-        <v>28562</v>
+        <v>11130</v>
       </c>
       <c r="E7" t="n">
-        <v>299557</v>
+        <v>70795</v>
       </c>
       <c r="F7" t="n">
-        <v>821232</v>
+        <v>125842</v>
       </c>
       <c r="G7" t="n">
-        <v>100248</v>
+        <v>11420</v>
       </c>
       <c r="H7" t="n">
-        <v>3545347</v>
+        <v>245334</v>
       </c>
       <c r="I7" t="n">
-        <v>302651</v>
+        <v>47043</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>44155</v>
+        <v>15141</v>
       </c>
       <c r="Z7" t="n">
-        <v>376853</v>
+        <v>79076</v>
       </c>
       <c r="AA7" t="n">
-        <v>947884</v>
+        <v>127747</v>
       </c>
       <c r="AB7" t="n">
-        <v>112924</v>
+        <v>11410</v>
       </c>
       <c r="AC7" t="n">
-        <v>3264326</v>
+        <v>229809</v>
       </c>
       <c r="AD7" t="n">
-        <v>351861</v>
+        <v>48464</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>244</v>
+        <v>35</v>
       </c>
       <c r="D8" t="n">
-        <v>1339</v>
+        <v>692</v>
       </c>
       <c r="E8" t="n">
-        <v>28558</v>
+        <v>8512</v>
       </c>
       <c r="F8" t="n">
-        <v>62211</v>
+        <v>15827</v>
       </c>
       <c r="G8" t="n">
-        <v>13106</v>
+        <v>2742</v>
       </c>
       <c r="H8" t="n">
-        <v>366923</v>
+        <v>57920</v>
       </c>
       <c r="I8" t="n">
-        <v>1462232</v>
+        <v>108077</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2657</v>
+        <v>1257</v>
       </c>
       <c r="Z8" t="n">
-        <v>38349</v>
+        <v>10113</v>
       </c>
       <c r="AA8" t="n">
-        <v>81023</v>
+        <v>18907</v>
       </c>
       <c r="AB8" t="n">
-        <v>16638</v>
+        <v>3052</v>
       </c>
       <c r="AC8" t="n">
-        <v>420054</v>
+        <v>58796</v>
       </c>
       <c r="AD8" t="n">
-        <v>1375892</v>
+        <v>101680</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
